--- a/data/raw/Usabilidad Power APP.xlsx
+++ b/data/raw/Usabilidad Power APP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\David\Documents\Maestría en Estudios del Comportamiento\tablero_pre_pos_intervencion\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EDEB14-D883-41FF-937D-1B2B4523ABF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD72675B-C26E-4703-BE17-E7F9AF5F343A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5031" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6465" uniqueCount="411">
   <si>
     <t>Título</t>
   </si>
@@ -922,6 +922,342 @@
   </si>
   <si>
     <t>Yessikaterine Uribe Arias</t>
+  </si>
+  <si>
+    <t>JUDLOPEZ@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Juan Diego Lopez Restrepo</t>
+  </si>
+  <si>
+    <t>jmanosas@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Juan Carlos Manosas Lopez</t>
+  </si>
+  <si>
+    <t>mmunera@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Mauricio Munera Palacio</t>
+  </si>
+  <si>
+    <t>ldurango@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Luz Adriana Durango Saenz</t>
+  </si>
+  <si>
+    <t>clarestr@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Clara Milena Restrepo Marin</t>
+  </si>
+  <si>
+    <t>nataestr@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Natalia Estrada Campiño</t>
+  </si>
+  <si>
+    <t>johanroj@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Johanna Elisa Rojas Olarte</t>
+  </si>
+  <si>
+    <t>RUCARDEN@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Ruben Dario Cardenas Henao</t>
+  </si>
+  <si>
+    <t>NGALLO@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Nathalie Gallo Giraldo</t>
+  </si>
+  <si>
+    <t>JFBRAVO@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Juan Felipe Bravo Velez</t>
+  </si>
+  <si>
+    <t>fabcorre@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Andres Correa Gonzalez</t>
+  </si>
+  <si>
+    <t>andherre@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Andres Felipe Herrera Gomez</t>
+  </si>
+  <si>
+    <t>moolaya@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Monica Olaya Herreño</t>
+  </si>
+  <si>
+    <t>mamurill@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Mariana Murillo Pemberthy</t>
+  </si>
+  <si>
+    <t>pmantill@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Paula Mantilla Correa</t>
+  </si>
+  <si>
+    <t>civilla@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Claudia Ines Villa Ramirez</t>
+  </si>
+  <si>
+    <t>cmjimene@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Carolina Maria Jimenez Gomez</t>
+  </si>
+  <si>
+    <t>femesa@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Felipe Mesa Baena</t>
+  </si>
+  <si>
+    <t>slezcano@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Santiago Lezcano Escobar</t>
+  </si>
+  <si>
+    <t>natorozc@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Natalia Andrea Orozco Zuluaga</t>
+  </si>
+  <si>
+    <t>lmontene@bancoagricola.com.sv</t>
+  </si>
+  <si>
+    <t>Lucia Renee Montenegro Montalvo</t>
+  </si>
+  <si>
+    <t>LCHERRER@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Luis Carlos Herrera Barrera</t>
+  </si>
+  <si>
+    <t>myepes@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Mauricio Yepes Builes</t>
+  </si>
+  <si>
+    <t>kgiraldo@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Katherine Giraldo Assis</t>
+  </si>
+  <si>
+    <t>MAISLOPE@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Maria Isabel Lopez Mejia</t>
+  </si>
+  <si>
+    <t>CALDANA@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Carlos Andres Aldana Gantiva</t>
+  </si>
+  <si>
+    <t>catabare@Bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Carlos Mauricio Tabares Cortes</t>
+  </si>
+  <si>
+    <t>DAVALENC@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>David Fernando Valencia Velasquez</t>
+  </si>
+  <si>
+    <t>vmorales@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Veronica Morales Luna</t>
+  </si>
+  <si>
+    <t>jlzapata@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Juan Camilo Londoño Zapata</t>
+  </si>
+  <si>
+    <t>FRMUNOZ@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Frank Ricardo Munoz Arbelaez</t>
+  </si>
+  <si>
+    <t>BIZQUIER@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Beatriz Elena Izquierdo Corrales</t>
+  </si>
+  <si>
+    <t>LAUHERRE@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Laura Herrera Rangel</t>
+  </si>
+  <si>
+    <t>amsoto@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Ana Maria Soto Peña</t>
+  </si>
+  <si>
+    <t>MILRIOS@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Milton Santiago Rios Pantoja</t>
+  </si>
+  <si>
+    <t>sbartoli@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Sergio Bartolini Botero</t>
+  </si>
+  <si>
+    <t>natamari@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Natalia Marin Zapata</t>
+  </si>
+  <si>
+    <t>laumarti@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Laura Isabel Martinez Eusse</t>
+  </si>
+  <si>
+    <t>jcandray@bancoagricola.com.sv</t>
+  </si>
+  <si>
+    <t>JOHANNA MICHELLE CANDRAY CALDERON</t>
+  </si>
+  <si>
+    <t>jpino@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Jeyny Heonir Pino Valencia</t>
+  </si>
+  <si>
+    <t>CATALIES@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Catalina Escobar Gallego</t>
+  </si>
+  <si>
+    <t>slopez@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Santiago Lopez Betancur</t>
+  </si>
+  <si>
+    <t>valet@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Valentina Torres Orozco</t>
+  </si>
+  <si>
+    <t>kportill@bancoagricola.com.sv</t>
+  </si>
+  <si>
+    <t>Karla Maria Portillo Erazo</t>
+  </si>
+  <si>
+    <t>catbetan@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Catalina Betancur Carvajal</t>
+  </si>
+  <si>
+    <t>dabedoya@Bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Darikza Fabina Bedoya Moreno</t>
+  </si>
+  <si>
+    <t>ILOAIZA@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Ivan Dario Loaiza Arcila</t>
+  </si>
+  <si>
+    <t>mvcastr@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Marcelino Vanegas Castro</t>
+  </si>
+  <si>
+    <t>lparang@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Laura Pineda Arango</t>
+  </si>
+  <si>
+    <t>lcarrasc@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Laura Stella Carrasco Cristancho</t>
+  </si>
+  <si>
+    <t>lromero@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Lucy Milena Romero Villa</t>
+  </si>
+  <si>
+    <t>NATGIL@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Natalia Gil Arias</t>
+  </si>
+  <si>
+    <t>syepes@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Sebastian Yepes Velez</t>
+  </si>
+  <si>
+    <t>neromero@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Nestor Josue Romero Jaller</t>
+  </si>
+  <si>
+    <t>pnperez@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>Paula Nataly Perez Duque</t>
+  </si>
+  <si>
+    <t>DACALLE@bancolombia.com.co</t>
+  </si>
+  <si>
+    <t>David Calle Esquivel</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I838"/>
+  <dimension ref="A1:I1077"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -23961,6 +24297,6459 @@
         <v>14</v>
       </c>
     </row>
+    <row r="839" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A839" s="4"/>
+      <c r="B839" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C839" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D839" s="6">
+        <v>46149.554861111108</v>
+      </c>
+      <c r="E839" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F839" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G839" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H839" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I839" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="840" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A840" s="9"/>
+      <c r="B840" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C840" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D840" s="11">
+        <v>46149.554861111108</v>
+      </c>
+      <c r="E840" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F840" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G840" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H840" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I840" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="841" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A841" s="4"/>
+      <c r="B841" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C841" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D841" s="6">
+        <v>46149.554861111108</v>
+      </c>
+      <c r="E841" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F841" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G841" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H841" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I841" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="842" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A842" s="9"/>
+      <c r="B842" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C842" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D842" s="11">
+        <v>46149.554861111108</v>
+      </c>
+      <c r="E842" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F842" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G842" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H842" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I842" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="843" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A843" s="4"/>
+      <c r="B843" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C843" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D843" s="6">
+        <v>46149.555555555555</v>
+      </c>
+      <c r="E843" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F843" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G843" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H843" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I843" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="844" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A844" s="9"/>
+      <c r="B844" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C844" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D844" s="11">
+        <v>46149.555555555555</v>
+      </c>
+      <c r="E844" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F844" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G844" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H844" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I844" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="845" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A845" s="9"/>
+      <c r="B845" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C845" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D845" s="11">
+        <v>46149.666666666664</v>
+      </c>
+      <c r="E845" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F845" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G845" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H845" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I845" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="846" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A846" s="4"/>
+      <c r="B846" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C846" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D846" s="6">
+        <v>46149.666666666664</v>
+      </c>
+      <c r="E846" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F846" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G846" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H846" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I846" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="847" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A847" s="9"/>
+      <c r="B847" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C847" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D847" s="11">
+        <v>46149.666666666664</v>
+      </c>
+      <c r="E847" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F847" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G847" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H847" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I847" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="848" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A848" s="4"/>
+      <c r="B848" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D848" s="6">
+        <v>46149.667361111111</v>
+      </c>
+      <c r="E848" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F848" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G848" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H848" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I848" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="849" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A849" s="9"/>
+      <c r="B849" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C849" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D849" s="11">
+        <v>46149.667361111111</v>
+      </c>
+      <c r="E849" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F849" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G849" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H849" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I849" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="850" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A850" s="4"/>
+      <c r="B850" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C850" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D850" s="6">
+        <v>46149.883333333331</v>
+      </c>
+      <c r="E850" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F850" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G850" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H850" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I850" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="851" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A851" s="9"/>
+      <c r="B851" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C851" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D851" s="11">
+        <v>46149.883333333331</v>
+      </c>
+      <c r="E851" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F851" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G851" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H851" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I851" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="852" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A852" s="4"/>
+      <c r="B852" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C852" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D852" s="6">
+        <v>46149.883333333331</v>
+      </c>
+      <c r="E852" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F852" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G852" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H852" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I852" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="853" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A853" s="9"/>
+      <c r="B853" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C853" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D853" s="11">
+        <v>46149.883333333331</v>
+      </c>
+      <c r="E853" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F853" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G853" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H853" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I853" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="854" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A854" s="4"/>
+      <c r="B854" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C854" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D854" s="6">
+        <v>46149.884027777778</v>
+      </c>
+      <c r="E854" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F854" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G854" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H854" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I854" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="855" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A855" s="9"/>
+      <c r="B855" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C855" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D855" s="11">
+        <v>46149.884027777778</v>
+      </c>
+      <c r="E855" s="12">
+        <v>46149</v>
+      </c>
+      <c r="F855" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G855" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H855" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I855" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="856" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A856" s="4"/>
+      <c r="B856" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C856" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D856" s="6">
+        <v>46150.722222222219</v>
+      </c>
+      <c r="E856" s="7">
+        <v>46150</v>
+      </c>
+      <c r="F856" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G856" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H856" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I856" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="857" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A857" s="9"/>
+      <c r="B857" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C857" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D857" s="11">
+        <v>46150.722222222219</v>
+      </c>
+      <c r="E857" s="12">
+        <v>46150</v>
+      </c>
+      <c r="F857" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G857" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H857" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I857" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="858" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A858" s="4"/>
+      <c r="B858" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C858" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D858" s="6">
+        <v>46150.722222222219</v>
+      </c>
+      <c r="E858" s="7">
+        <v>46150</v>
+      </c>
+      <c r="F858" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G858" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H858" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I858" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="859" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A859" s="9"/>
+      <c r="B859" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C859" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D859" s="11">
+        <v>46150.722222222219</v>
+      </c>
+      <c r="E859" s="12">
+        <v>46150</v>
+      </c>
+      <c r="F859" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G859" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H859" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I859" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="860" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A860" s="4"/>
+      <c r="B860" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C860" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D860" s="6">
+        <v>46150.742361111108</v>
+      </c>
+      <c r="E860" s="7">
+        <v>46150</v>
+      </c>
+      <c r="F860" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G860" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H860" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I860" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="861" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A861" s="9"/>
+      <c r="B861" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C861" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D861" s="11">
+        <v>46150.742361111108</v>
+      </c>
+      <c r="E861" s="12">
+        <v>46150</v>
+      </c>
+      <c r="F861" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G861" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H861" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I861" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="862" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A862" s="4"/>
+      <c r="B862" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C862" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D862" s="6">
+        <v>46150.744444444441</v>
+      </c>
+      <c r="E862" s="7">
+        <v>46150</v>
+      </c>
+      <c r="F862" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G862" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H862" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I862" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="863" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A863" s="9"/>
+      <c r="B863" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C863" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D863" s="11">
+        <v>46150.744444444441</v>
+      </c>
+      <c r="E863" s="12">
+        <v>46150</v>
+      </c>
+      <c r="F863" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G863" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H863" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I863" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="864" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A864" s="4"/>
+      <c r="B864" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C864" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D864" s="6">
+        <v>46151.943055555559</v>
+      </c>
+      <c r="E864" s="7">
+        <v>46151</v>
+      </c>
+      <c r="F864" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G864" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H864" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I864" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A865" s="9"/>
+      <c r="B865" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C865" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D865" s="11">
+        <v>46151.945138888892</v>
+      </c>
+      <c r="E865" s="12">
+        <v>46151</v>
+      </c>
+      <c r="F865" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G865" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H865" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I865" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A866" s="4"/>
+      <c r="B866" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C866" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D866" s="6">
+        <v>46151.947222222225</v>
+      </c>
+      <c r="E866" s="7">
+        <v>46151</v>
+      </c>
+      <c r="F866" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G866" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H866" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I866" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A867" s="9"/>
+      <c r="B867" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C867" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D867" s="11">
+        <v>46151.947916666664</v>
+      </c>
+      <c r="E867" s="12">
+        <v>46151</v>
+      </c>
+      <c r="F867" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G867" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H867" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I867" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A868" s="4"/>
+      <c r="B868" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C868" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D868" s="6">
+        <v>46151.965277777781</v>
+      </c>
+      <c r="E868" s="7">
+        <v>46151</v>
+      </c>
+      <c r="F868" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G868" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H868" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I868" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A869" s="9"/>
+      <c r="B869" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C869" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D869" s="11">
+        <v>46151.96597222222</v>
+      </c>
+      <c r="E869" s="12">
+        <v>46151</v>
+      </c>
+      <c r="F869" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G869" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H869" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I869" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A870" s="4"/>
+      <c r="B870" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C870" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D870" s="6">
+        <v>46153.648611111108</v>
+      </c>
+      <c r="E870" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F870" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G870" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H870" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I870" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A871" s="9"/>
+      <c r="B871" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C871" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D871" s="11">
+        <v>46153.649305555555</v>
+      </c>
+      <c r="E871" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F871" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G871" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H871" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I871" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A872" s="4"/>
+      <c r="B872" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C872" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D872" s="6">
+        <v>46153.649305555555</v>
+      </c>
+      <c r="E872" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F872" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G872" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H872" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I872" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A873" s="9"/>
+      <c r="B873" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C873" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D873" s="11">
+        <v>46153.65</v>
+      </c>
+      <c r="E873" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F873" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G873" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H873" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I873" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A874" s="4"/>
+      <c r="B874" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C874" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D874" s="6">
+        <v>46153.65</v>
+      </c>
+      <c r="E874" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F874" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G874" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H874" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I874" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A875" s="9"/>
+      <c r="B875" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C875" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D875" s="11">
+        <v>46153.652083333334</v>
+      </c>
+      <c r="E875" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F875" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G875" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H875" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I875" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A876" s="4"/>
+      <c r="B876" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C876" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D876" s="6">
+        <v>46153.652083333334</v>
+      </c>
+      <c r="E876" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F876" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G876" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H876" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I876" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A877" s="9"/>
+      <c r="B877" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C877" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D877" s="11">
+        <v>46153.652083333334</v>
+      </c>
+      <c r="E877" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F877" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G877" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H877" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I877" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A878" s="4"/>
+      <c r="B878" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C878" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D878" s="6">
+        <v>46153.654861111114</v>
+      </c>
+      <c r="E878" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F878" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G878" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H878" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I878" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A879" s="9"/>
+      <c r="B879" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C879" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="D879" s="11">
+        <v>46153.654861111114</v>
+      </c>
+      <c r="E879" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F879" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G879" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H879" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I879" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A880" s="4"/>
+      <c r="B880" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C880" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D880" s="6">
+        <v>46153.654861111114</v>
+      </c>
+      <c r="E880" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F880" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G880" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H880" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I880" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A881" s="9"/>
+      <c r="B881" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C881" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D881" s="11">
+        <v>46153.655555555553</v>
+      </c>
+      <c r="E881" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F881" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G881" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H881" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I881" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A882" s="4"/>
+      <c r="B882" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C882" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D882" s="6">
+        <v>46153.656944444447</v>
+      </c>
+      <c r="E882" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F882" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G882" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H882" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I882" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A883" s="9"/>
+      <c r="B883" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C883" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D883" s="11">
+        <v>46153.656944444447</v>
+      </c>
+      <c r="E883" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F883" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G883" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H883" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I883" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A884" s="4"/>
+      <c r="B884" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C884" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D884" s="6">
+        <v>46153.658333333333</v>
+      </c>
+      <c r="E884" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F884" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G884" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H884" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I884" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A885" s="9"/>
+      <c r="B885" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C885" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D885" s="11">
+        <v>46153.658333333333</v>
+      </c>
+      <c r="E885" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F885" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G885" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H885" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I885" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A886" s="4"/>
+      <c r="B886" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C886" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D886" s="6">
+        <v>46153.65902777778</v>
+      </c>
+      <c r="E886" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F886" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G886" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H886" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I886" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A887" s="9"/>
+      <c r="B887" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C887" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D887" s="11">
+        <v>46153.65902777778</v>
+      </c>
+      <c r="E887" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F887" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G887" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H887" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I887" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A888" s="4"/>
+      <c r="B888" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C888" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D888" s="6">
+        <v>46153.65902777778</v>
+      </c>
+      <c r="E888" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F888" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G888" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H888" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I888" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A889" s="9"/>
+      <c r="B889" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C889" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D889" s="11">
+        <v>46153.65902777778</v>
+      </c>
+      <c r="E889" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F889" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G889" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H889" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I889" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A890" s="4"/>
+      <c r="B890" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C890" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D890" s="6">
+        <v>46153.65902777778</v>
+      </c>
+      <c r="E890" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F890" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G890" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H890" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I890" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A891" s="9"/>
+      <c r="B891" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C891" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D891" s="11">
+        <v>46153.65902777778</v>
+      </c>
+      <c r="E891" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F891" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G891" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H891" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I891" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A892" s="4"/>
+      <c r="B892" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C892" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D892" s="6">
+        <v>46153.659722222219</v>
+      </c>
+      <c r="E892" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F892" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G892" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H892" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I892" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A893" s="9"/>
+      <c r="B893" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C893" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D893" s="11">
+        <v>46153.660416666666</v>
+      </c>
+      <c r="E893" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F893" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G893" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H893" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I893" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A894" s="4"/>
+      <c r="B894" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C894" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D894" s="6">
+        <v>46153.660416666666</v>
+      </c>
+      <c r="E894" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F894" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G894" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H894" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I894" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A895" s="9"/>
+      <c r="B895" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C895" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D895" s="11">
+        <v>46153.665972222225</v>
+      </c>
+      <c r="E895" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F895" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G895" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H895" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I895" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A896" s="4"/>
+      <c r="B896" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C896" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D896" s="6">
+        <v>46153.666666666664</v>
+      </c>
+      <c r="E896" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F896" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G896" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H896" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I896" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="897" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A897" s="9"/>
+      <c r="B897" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C897" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="D897" s="11">
+        <v>46153.667361111111</v>
+      </c>
+      <c r="E897" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F897" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G897" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H897" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I897" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="898" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A898" s="4"/>
+      <c r="B898" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C898" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D898" s="6">
+        <v>46153.667361111111</v>
+      </c>
+      <c r="E898" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F898" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G898" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H898" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I898" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="899" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A899" s="9"/>
+      <c r="B899" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C899" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D899" s="11">
+        <v>46153.668749999997</v>
+      </c>
+      <c r="E899" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F899" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G899" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H899" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I899" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="900" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A900" s="4"/>
+      <c r="B900" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C900" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D900" s="6">
+        <v>46153.669444444444</v>
+      </c>
+      <c r="E900" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F900" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G900" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H900" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I900" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="901" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A901" s="9"/>
+      <c r="B901" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C901" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D901" s="11">
+        <v>46153.67083333333</v>
+      </c>
+      <c r="E901" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F901" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G901" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H901" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I901" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="902" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A902" s="4"/>
+      <c r="B902" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C902" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D902" s="6">
+        <v>46153.671527777777</v>
+      </c>
+      <c r="E902" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F902" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G902" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H902" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I902" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="903" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A903" s="9"/>
+      <c r="B903" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C903" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D903" s="11">
+        <v>46153.675000000003</v>
+      </c>
+      <c r="E903" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F903" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G903" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H903" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I903" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="904" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A904" s="4"/>
+      <c r="B904" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C904" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D904" s="6">
+        <v>46153.675000000003</v>
+      </c>
+      <c r="E904" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F904" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G904" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H904" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I904" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="905" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A905" s="9"/>
+      <c r="B905" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C905" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D905" s="11">
+        <v>46153.675000000003</v>
+      </c>
+      <c r="E905" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F905" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G905" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H905" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I905" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="906" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A906" s="4"/>
+      <c r="B906" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C906" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D906" s="6">
+        <v>46153.680555555555</v>
+      </c>
+      <c r="E906" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F906" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G906" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H906" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I906" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="907" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A907" s="9"/>
+      <c r="B907" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C907" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="D907" s="11">
+        <v>46153.680555555555</v>
+      </c>
+      <c r="E907" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F907" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G907" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H907" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I907" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="908" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A908" s="4"/>
+      <c r="B908" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C908" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D908" s="6">
+        <v>46153.681250000001</v>
+      </c>
+      <c r="E908" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F908" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G908" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H908" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I908" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="909" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A909" s="9"/>
+      <c r="B909" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C909" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D909" s="11">
+        <v>46153.681944444441</v>
+      </c>
+      <c r="E909" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F909" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G909" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H909" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I909" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="910" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A910" s="4"/>
+      <c r="B910" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C910" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D910" s="6">
+        <v>46153.682638888888</v>
+      </c>
+      <c r="E910" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F910" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G910" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H910" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I910" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="911" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A911" s="9"/>
+      <c r="B911" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C911" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D911" s="11">
+        <v>46153.683333333334</v>
+      </c>
+      <c r="E911" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F911" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G911" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H911" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I911" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="912" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A912" s="4"/>
+      <c r="B912" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C912" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D912" s="6">
+        <v>46153.683333333334</v>
+      </c>
+      <c r="E912" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F912" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G912" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H912" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I912" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="913" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A913" s="9"/>
+      <c r="B913" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C913" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D913" s="11">
+        <v>46153.684027777781</v>
+      </c>
+      <c r="E913" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F913" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G913" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H913" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I913" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="914" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A914" s="4"/>
+      <c r="B914" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C914" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D914" s="6">
+        <v>46153.686805555553</v>
+      </c>
+      <c r="E914" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F914" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G914" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H914" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I914" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="915" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A915" s="9"/>
+      <c r="B915" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C915" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D915" s="11">
+        <v>46153.688888888886</v>
+      </c>
+      <c r="E915" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F915" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G915" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H915" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I915" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="916" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A916" s="4"/>
+      <c r="B916" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C916" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D916" s="6">
+        <v>46153.688888888886</v>
+      </c>
+      <c r="E916" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F916" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G916" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H916" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I916" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="917" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A917" s="9"/>
+      <c r="B917" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C917" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D917" s="11">
+        <v>46153.696527777778</v>
+      </c>
+      <c r="E917" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F917" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G917" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H917" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I917" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="918" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A918" s="4"/>
+      <c r="B918" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C918" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D918" s="6">
+        <v>46153.696527777778</v>
+      </c>
+      <c r="E918" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F918" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G918" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H918" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I918" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="919" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A919" s="9"/>
+      <c r="B919" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C919" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D919" s="11">
+        <v>46153.696527777778</v>
+      </c>
+      <c r="E919" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F919" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G919" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H919" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I919" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="920" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A920" s="4"/>
+      <c r="B920" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C920" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="D920" s="6">
+        <v>46153.697222222225</v>
+      </c>
+      <c r="E920" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F920" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G920" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H920" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I920" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="921" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A921" s="9"/>
+      <c r="B921" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C921" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D921" s="11">
+        <v>46153.697222222225</v>
+      </c>
+      <c r="E921" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F921" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G921" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H921" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I921" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="922" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A922" s="4"/>
+      <c r="B922" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C922" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D922" s="6">
+        <v>46153.70416666667</v>
+      </c>
+      <c r="E922" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F922" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G922" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H922" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I922" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="923" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A923" s="9"/>
+      <c r="B923" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C923" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D923" s="11">
+        <v>46153.705555555556</v>
+      </c>
+      <c r="E923" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F923" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G923" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H923" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I923" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="924" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A924" s="4"/>
+      <c r="B924" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C924" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D924" s="6">
+        <v>46153.707638888889</v>
+      </c>
+      <c r="E924" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F924" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G924" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H924" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I924" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="925" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A925" s="9"/>
+      <c r="B925" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C925" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D925" s="11">
+        <v>46153.708333333336</v>
+      </c>
+      <c r="E925" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F925" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G925" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H925" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I925" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="926" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A926" s="4"/>
+      <c r="B926" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C926" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D926" s="6">
+        <v>46153.709027777775</v>
+      </c>
+      <c r="E926" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F926" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G926" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H926" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I926" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="927" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A927" s="9"/>
+      <c r="B927" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C927" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D927" s="11">
+        <v>46153.709027777775</v>
+      </c>
+      <c r="E927" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F927" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G927" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H927" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I927" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="928" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A928" s="4"/>
+      <c r="B928" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C928" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D928" s="6">
+        <v>46153.711111111108</v>
+      </c>
+      <c r="E928" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F928" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G928" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H928" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I928" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="929" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A929" s="9"/>
+      <c r="B929" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C929" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D929" s="11">
+        <v>46153.711111111108</v>
+      </c>
+      <c r="E929" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F929" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G929" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H929" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I929" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="930" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A930" s="4"/>
+      <c r="B930" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C930" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D930" s="6">
+        <v>46153.711111111108</v>
+      </c>
+      <c r="E930" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F930" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G930" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H930" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I930" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A931" s="9"/>
+      <c r="B931" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C931" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D931" s="11">
+        <v>46153.715277777781</v>
+      </c>
+      <c r="E931" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F931" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G931" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H931" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I931" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A932" s="4"/>
+      <c r="B932" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C932" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D932" s="6">
+        <v>46153.718055555553</v>
+      </c>
+      <c r="E932" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F932" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G932" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H932" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I932" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A933" s="9"/>
+      <c r="B933" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C933" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D933" s="11">
+        <v>46153.71875</v>
+      </c>
+      <c r="E933" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F933" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G933" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H933" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I933" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A934" s="4"/>
+      <c r="B934" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C934" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D934" s="6">
+        <v>46153.71875</v>
+      </c>
+      <c r="E934" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F934" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G934" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H934" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I934" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A935" s="9"/>
+      <c r="B935" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="C935" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="D935" s="11">
+        <v>46153.723611111112</v>
+      </c>
+      <c r="E935" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F935" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G935" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H935" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I935" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A936" s="4"/>
+      <c r="B936" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C936" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D936" s="6">
+        <v>46153.727083333331</v>
+      </c>
+      <c r="E936" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F936" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G936" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H936" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I936" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A937" s="9"/>
+      <c r="B937" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C937" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D937" s="11">
+        <v>46153.727083333331</v>
+      </c>
+      <c r="E937" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F937" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G937" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H937" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I937" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A938" s="4"/>
+      <c r="B938" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C938" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D938" s="6">
+        <v>46153.727083333331</v>
+      </c>
+      <c r="E938" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F938" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G938" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H938" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I938" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A939" s="9"/>
+      <c r="B939" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C939" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D939" s="11">
+        <v>46153.727777777778</v>
+      </c>
+      <c r="E939" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F939" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G939" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H939" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I939" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A940" s="4"/>
+      <c r="B940" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C940" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D940" s="6">
+        <v>46153.734027777777</v>
+      </c>
+      <c r="E940" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F940" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G940" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H940" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I940" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A941" s="9"/>
+      <c r="B941" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C941" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="D941" s="11">
+        <v>46153.734027777777</v>
+      </c>
+      <c r="E941" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F941" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G941" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H941" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I941" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A942" s="4"/>
+      <c r="B942" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C942" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D942" s="6">
+        <v>46153.734027777777</v>
+      </c>
+      <c r="E942" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F942" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G942" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H942" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I942" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A943" s="9"/>
+      <c r="B943" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C943" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D943" s="11">
+        <v>46153.741666666669</v>
+      </c>
+      <c r="E943" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F943" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G943" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H943" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I943" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A944" s="4"/>
+      <c r="B944" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C944" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D944" s="6">
+        <v>46153.741666666669</v>
+      </c>
+      <c r="E944" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F944" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G944" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H944" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I944" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A945" s="9"/>
+      <c r="B945" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C945" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D945" s="11">
+        <v>46153.741666666669</v>
+      </c>
+      <c r="E945" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F945" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G945" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H945" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I945" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A946" s="4"/>
+      <c r="B946" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C946" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D946" s="6">
+        <v>46153.741666666669</v>
+      </c>
+      <c r="E946" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F946" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G946" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H946" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I946" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A947" s="9"/>
+      <c r="B947" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C947" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D947" s="11">
+        <v>46153.741666666669</v>
+      </c>
+      <c r="E947" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F947" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G947" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H947" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I947" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A948" s="4"/>
+      <c r="B948" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C948" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D948" s="6">
+        <v>46153.742361111108</v>
+      </c>
+      <c r="E948" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F948" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G948" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H948" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I948" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A949" s="9"/>
+      <c r="B949" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C949" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D949" s="11">
+        <v>46153.743055555555</v>
+      </c>
+      <c r="E949" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F949" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G949" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H949" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I949" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A950" s="4"/>
+      <c r="B950" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C950" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D950" s="6">
+        <v>46153.743750000001</v>
+      </c>
+      <c r="E950" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F950" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G950" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H950" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I950" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A951" s="9"/>
+      <c r="B951" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C951" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="D951" s="11">
+        <v>46153.85833333333</v>
+      </c>
+      <c r="E951" s="12">
+        <v>46153</v>
+      </c>
+      <c r="F951" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G951" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H951" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I951" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A952" s="4"/>
+      <c r="B952" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C952" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D952" s="6">
+        <v>46153.898611111108</v>
+      </c>
+      <c r="E952" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F952" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G952" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H952" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I952" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A953" s="9"/>
+      <c r="B953" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C953" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D953" s="11">
+        <v>46154.343055555553</v>
+      </c>
+      <c r="E953" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F953" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G953" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H953" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I953" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A954" s="4"/>
+      <c r="B954" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C954" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D954" s="6">
+        <v>46154.34375</v>
+      </c>
+      <c r="E954" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F954" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G954" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H954" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I954" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A955" s="9"/>
+      <c r="B955" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C955" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D955" s="11">
+        <v>46154.34375</v>
+      </c>
+      <c r="E955" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F955" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G955" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H955" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I955" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A956" s="4"/>
+      <c r="B956" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C956" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D956" s="6">
+        <v>46154.34375</v>
+      </c>
+      <c r="E956" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F956" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G956" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H956" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I956" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A957" s="9"/>
+      <c r="B957" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C957" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D957" s="11">
+        <v>46154.347916666666</v>
+      </c>
+      <c r="E957" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F957" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G957" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H957" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I957" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A958" s="4"/>
+      <c r="B958" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C958" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D958" s="6">
+        <v>46154.347916666666</v>
+      </c>
+      <c r="E958" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F958" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G958" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H958" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I958" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A959" s="9"/>
+      <c r="B959" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C959" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D959" s="11">
+        <v>46154.356249999997</v>
+      </c>
+      <c r="E959" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F959" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G959" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H959" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I959" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A960" s="4"/>
+      <c r="B960" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C960" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D960" s="6">
+        <v>46154.356944444444</v>
+      </c>
+      <c r="E960" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F960" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G960" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H960" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I960" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A961" s="9"/>
+      <c r="B961" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C961" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D961" s="11">
+        <v>46154.356944444444</v>
+      </c>
+      <c r="E961" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F961" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G961" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H961" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I961" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A962" s="4"/>
+      <c r="B962" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C962" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D962" s="6">
+        <v>46154.365972222222</v>
+      </c>
+      <c r="E962" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F962" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G962" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H962" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I962" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A963" s="9"/>
+      <c r="B963" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C963" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="D963" s="11">
+        <v>46154.365972222222</v>
+      </c>
+      <c r="E963" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F963" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G963" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H963" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I963" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A964" s="4"/>
+      <c r="B964" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C964" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D964" s="6">
+        <v>46154.365972222222</v>
+      </c>
+      <c r="E964" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F964" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G964" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H964" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I964" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A965" s="9"/>
+      <c r="B965" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C965" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D965" s="11">
+        <v>46154.384722222225</v>
+      </c>
+      <c r="E965" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F965" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G965" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H965" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I965" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A966" s="4"/>
+      <c r="B966" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C966" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D966" s="6">
+        <v>46154.384722222225</v>
+      </c>
+      <c r="E966" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F966" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G966" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H966" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I966" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A967" s="9"/>
+      <c r="B967" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C967" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D967" s="11">
+        <v>46154.390972222223</v>
+      </c>
+      <c r="E967" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F967" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G967" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H967" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I967" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A968" s="4"/>
+      <c r="B968" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C968" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D968" s="6">
+        <v>46154.392361111109</v>
+      </c>
+      <c r="E968" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F968" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G968" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H968" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I968" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A969" s="9"/>
+      <c r="B969" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="C969" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D969" s="11">
+        <v>46154.392361111109</v>
+      </c>
+      <c r="E969" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F969" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G969" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H969" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I969" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A970" s="4"/>
+      <c r="B970" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C970" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D970" s="6">
+        <v>46154.393750000003</v>
+      </c>
+      <c r="E970" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F970" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G970" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H970" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I970" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A971" s="9"/>
+      <c r="B971" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C971" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D971" s="11">
+        <v>46154.394444444442</v>
+      </c>
+      <c r="E971" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F971" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G971" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H971" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I971" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A972" s="4"/>
+      <c r="B972" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C972" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D972" s="6">
+        <v>46154.396527777775</v>
+      </c>
+      <c r="E972" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F972" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G972" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H972" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I972" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A973" s="9"/>
+      <c r="B973" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C973" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D973" s="11">
+        <v>46154.397222222222</v>
+      </c>
+      <c r="E973" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F973" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G973" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H973" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I973" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A974" s="4"/>
+      <c r="B974" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C974" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D974" s="6">
+        <v>46154.402777777781</v>
+      </c>
+      <c r="E974" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F974" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G974" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H974" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I974" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A975" s="9"/>
+      <c r="B975" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C975" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D975" s="11">
+        <v>46154.445138888892</v>
+      </c>
+      <c r="E975" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F975" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G975" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H975" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I975" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A976" s="4"/>
+      <c r="B976" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C976" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D976" s="6">
+        <v>46154.47152777778</v>
+      </c>
+      <c r="E976" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F976" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G976" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H976" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I976" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A977" s="9"/>
+      <c r="B977" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="C977" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D977" s="11">
+        <v>46154.47152777778</v>
+      </c>
+      <c r="E977" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F977" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G977" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H977" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I977" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A978" s="4"/>
+      <c r="B978" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C978" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D978" s="6">
+        <v>46154.47152777778</v>
+      </c>
+      <c r="E978" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F978" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G978" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H978" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I978" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A979" s="9"/>
+      <c r="B979" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C979" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D979" s="11">
+        <v>46154.490277777775</v>
+      </c>
+      <c r="E979" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F979" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G979" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H979" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I979" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A980" s="4"/>
+      <c r="B980" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C980" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D980" s="6">
+        <v>46154.490277777775</v>
+      </c>
+      <c r="E980" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F980" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G980" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H980" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I980" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A981" s="9"/>
+      <c r="B981" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C981" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D981" s="11">
+        <v>46154.490972222222</v>
+      </c>
+      <c r="E981" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F981" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G981" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H981" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I981" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A982" s="4"/>
+      <c r="B982" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C982" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D982" s="6">
+        <v>46154.490972222222</v>
+      </c>
+      <c r="E982" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F982" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G982" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H982" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I982" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A983" s="9"/>
+      <c r="B983" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C983" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D983" s="11">
+        <v>46154.512499999997</v>
+      </c>
+      <c r="E983" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F983" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G983" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H983" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I983" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A984" s="4"/>
+      <c r="B984" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C984" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D984" s="6">
+        <v>46154.548611111109</v>
+      </c>
+      <c r="E984" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F984" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G984" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H984" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I984" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A985" s="9"/>
+      <c r="B985" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C985" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D985" s="11">
+        <v>46154.579861111109</v>
+      </c>
+      <c r="E985" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F985" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G985" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H985" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I985" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A986" s="4"/>
+      <c r="B986" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C986" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D986" s="6">
+        <v>46154.579861111109</v>
+      </c>
+      <c r="E986" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F986" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G986" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H986" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I986" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A987" s="9"/>
+      <c r="B987" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="C987" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="D987" s="11">
+        <v>46154.59375</v>
+      </c>
+      <c r="E987" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F987" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G987" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H987" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I987" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A988" s="4"/>
+      <c r="B988" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C988" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D988" s="6">
+        <v>46154.59375</v>
+      </c>
+      <c r="E988" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F988" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G988" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H988" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I988" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A989" s="9"/>
+      <c r="B989" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C989" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D989" s="11">
+        <v>46154.640972222223</v>
+      </c>
+      <c r="E989" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F989" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G989" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H989" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I989" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A990" s="4"/>
+      <c r="B990" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C990" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D990" s="6">
+        <v>46154.642361111109</v>
+      </c>
+      <c r="E990" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F990" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G990" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H990" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I990" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A991" s="9"/>
+      <c r="B991" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C991" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D991" s="11">
+        <v>46154.642361111109</v>
+      </c>
+      <c r="E991" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F991" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G991" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H991" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I991" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A992" s="4"/>
+      <c r="B992" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C992" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D992" s="6">
+        <v>46154.644444444442</v>
+      </c>
+      <c r="E992" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F992" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G992" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H992" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I992" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A993" s="9"/>
+      <c r="B993" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C993" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D993" s="11">
+        <v>46154.644444444442</v>
+      </c>
+      <c r="E993" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F993" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G993" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H993" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I993" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A994" s="4"/>
+      <c r="B994" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C994" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D994" s="6">
+        <v>46154.646527777775</v>
+      </c>
+      <c r="E994" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F994" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G994" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H994" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I994" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A995" s="9"/>
+      <c r="B995" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C995" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D995" s="11">
+        <v>46154.646527777775</v>
+      </c>
+      <c r="E995" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F995" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G995" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H995" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I995" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A996" s="4"/>
+      <c r="B996" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C996" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D996" s="6">
+        <v>46154.646527777775</v>
+      </c>
+      <c r="E996" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F996" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G996" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H996" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I996" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A997" s="9"/>
+      <c r="B997" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C997" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D997" s="11">
+        <v>46154.646527777775</v>
+      </c>
+      <c r="E997" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F997" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G997" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H997" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I997" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A998" s="4"/>
+      <c r="B998" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C998" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D998" s="6">
+        <v>46154.652777777781</v>
+      </c>
+      <c r="E998" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F998" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G998" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H998" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I998" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A999" s="9"/>
+      <c r="B999" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="C999" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D999" s="11">
+        <v>46154.656944444447</v>
+      </c>
+      <c r="E999" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F999" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G999" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H999" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I999" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1000" s="4"/>
+      <c r="B1000" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C1000" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1000" s="6">
+        <v>46154.656944444447</v>
+      </c>
+      <c r="E1000" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F1000" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1000" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1000" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1000" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1001" s="9"/>
+      <c r="B1001" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="C1001" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1001" s="11">
+        <v>46154.661111111112</v>
+      </c>
+      <c r="E1001" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F1001" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1001" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1001" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1001" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1002" s="4"/>
+      <c r="B1002" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C1002" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1002" s="6">
+        <v>46154.665277777778</v>
+      </c>
+      <c r="E1002" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F1002" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1002" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1002" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1002" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1003" s="9"/>
+      <c r="B1003" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1003" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1003" s="11">
+        <v>46154.665277777778</v>
+      </c>
+      <c r="E1003" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F1003" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1003" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1003" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1003" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1004" s="4"/>
+      <c r="B1004" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1004" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1004" s="6">
+        <v>46154.665972222225</v>
+      </c>
+      <c r="E1004" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F1004" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1004" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1004" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1004" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1005" s="9"/>
+      <c r="B1005" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1005" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1005" s="11">
+        <v>46154.880555555559</v>
+      </c>
+      <c r="E1005" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F1005" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1005" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1005" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1005" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1006" s="4"/>
+      <c r="B1006" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1006" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1006" s="6">
+        <v>46154.880555555559</v>
+      </c>
+      <c r="E1006" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F1006" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1006" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1006" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1006" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1007" s="9"/>
+      <c r="B1007" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1007" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1007" s="11">
+        <v>46154.881249999999</v>
+      </c>
+      <c r="E1007" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F1007" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1007" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1007" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1007" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1008" s="4"/>
+      <c r="B1008" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1008" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1008" s="6">
+        <v>46154.881249999999</v>
+      </c>
+      <c r="E1008" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F1008" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1008" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1008" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1008" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1009" s="9"/>
+      <c r="B1009" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1009" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1009" s="11">
+        <v>46154.881249999999</v>
+      </c>
+      <c r="E1009" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F1009" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1009" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1009" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1009" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1010" s="4"/>
+      <c r="B1010" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1010" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1010" s="6">
+        <v>46154.89166666667</v>
+      </c>
+      <c r="E1010" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F1010" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1010" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1010" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1010" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1011" s="9"/>
+      <c r="B1011" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1011" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1011" s="11">
+        <v>46154.89166666667</v>
+      </c>
+      <c r="E1011" s="12">
+        <v>46154</v>
+      </c>
+      <c r="F1011" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1011" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1011" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1011" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1012" s="4"/>
+      <c r="B1012" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1012" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1012" s="6">
+        <v>46154.89166666667</v>
+      </c>
+      <c r="E1012" s="7">
+        <v>46154</v>
+      </c>
+      <c r="F1012" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1012" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1012" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1012" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1013" s="9"/>
+      <c r="B1013" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1013" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1013" s="11">
+        <v>46155.35833333333</v>
+      </c>
+      <c r="E1013" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1013" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1013" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1013" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1013" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1014" s="4"/>
+      <c r="B1014" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1014" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="D1014" s="6">
+        <v>46155.359027777777</v>
+      </c>
+      <c r="E1014" s="7">
+        <v>46155</v>
+      </c>
+      <c r="F1014" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1014" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1014" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1014" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1015" s="9"/>
+      <c r="B1015" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1015" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1015" s="11">
+        <v>46155.392361111109</v>
+      </c>
+      <c r="E1015" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1015" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1015" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1015" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1015" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1016" s="4"/>
+      <c r="B1016" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C1016" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D1016" s="6">
+        <v>46155.442361111112</v>
+      </c>
+      <c r="E1016" s="7">
+        <v>46155</v>
+      </c>
+      <c r="F1016" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1016" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1016" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1016" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1017" s="9"/>
+      <c r="B1017" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1017" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1017" s="11">
+        <v>46155.445833333331</v>
+      </c>
+      <c r="E1017" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1017" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1017" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1017" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1017" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1018" s="4"/>
+      <c r="B1018" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1018" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1018" s="6">
+        <v>46155.445833333331</v>
+      </c>
+      <c r="E1018" s="7">
+        <v>46155</v>
+      </c>
+      <c r="F1018" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1018" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1018" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1018" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1019" s="9"/>
+      <c r="B1019" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1019" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1019" s="11">
+        <v>46155.445833333331</v>
+      </c>
+      <c r="E1019" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1019" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1019" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1019" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1019" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1020" s="4"/>
+      <c r="B1020" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1020" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1020" s="6">
+        <v>46155.445833333331</v>
+      </c>
+      <c r="E1020" s="7">
+        <v>46155</v>
+      </c>
+      <c r="F1020" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1020" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1020" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1020" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1021" s="9"/>
+      <c r="B1021" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1021" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="D1021" s="11">
+        <v>46155.467361111114</v>
+      </c>
+      <c r="E1021" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1021" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1021" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1021" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1021" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1022" s="4"/>
+      <c r="B1022" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1022" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1022" s="6">
+        <v>46155.47152777778</v>
+      </c>
+      <c r="E1022" s="7">
+        <v>46155</v>
+      </c>
+      <c r="F1022" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1022" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1022" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1022" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1023" s="9"/>
+      <c r="B1023" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1023" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1023" s="11">
+        <v>46155.65902777778</v>
+      </c>
+      <c r="E1023" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1023" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1023" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1023" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1023" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1024" s="4"/>
+      <c r="B1024" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1024" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1024" s="6">
+        <v>46155.65902777778</v>
+      </c>
+      <c r="E1024" s="7">
+        <v>46155</v>
+      </c>
+      <c r="F1024" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1024" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1024" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1024" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1025" s="9"/>
+      <c r="B1025" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1025" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1025" s="11">
+        <v>46155.65902777778</v>
+      </c>
+      <c r="E1025" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1025" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1025" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1025" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1025" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1026" s="4"/>
+      <c r="B1026" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1026" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1026" s="6">
+        <v>46155.659722222219</v>
+      </c>
+      <c r="E1026" s="7">
+        <v>46155</v>
+      </c>
+      <c r="F1026" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1026" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1026" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1026" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1027" s="9"/>
+      <c r="B1027" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1027" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1027" s="11">
+        <v>46155.659722222219</v>
+      </c>
+      <c r="E1027" s="12">
+        <v>46155</v>
+      </c>
+      <c r="F1027" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1027" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1027" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1027" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1028" s="4"/>
+      <c r="B1028" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1028" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D1028" s="6">
+        <v>46156.488194444442</v>
+      </c>
+      <c r="E1028" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1028" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1028" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1028" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1028" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1029" s="9"/>
+      <c r="B1029" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1029" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1029" s="11">
+        <v>46156.498611111114</v>
+      </c>
+      <c r="E1029" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1029" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1029" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1029" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1029" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1030" s="4"/>
+      <c r="B1030" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1030" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1030" s="6">
+        <v>46156.505555555559</v>
+      </c>
+      <c r="E1030" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1030" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1030" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1030" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1030" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1031" s="9"/>
+      <c r="B1031" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1031" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1031" s="11">
+        <v>46156.506249999999</v>
+      </c>
+      <c r="E1031" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1031" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1031" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1031" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1031" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1032" s="4"/>
+      <c r="B1032" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1032" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1032" s="6">
+        <v>46156.506249999999</v>
+      </c>
+      <c r="E1032" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1032" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1032" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1032" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1032" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1033" s="9"/>
+      <c r="B1033" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1033" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1033" s="11">
+        <v>46156.506944444445</v>
+      </c>
+      <c r="E1033" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1033" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1033" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1033" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1033" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1034" s="4"/>
+      <c r="B1034" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1034" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1034" s="6">
+        <v>46156.506944444445</v>
+      </c>
+      <c r="E1034" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1034" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1034" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1034" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1034" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1035" s="9"/>
+      <c r="B1035" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1035" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1035" s="11">
+        <v>46156.580555555556</v>
+      </c>
+      <c r="E1035" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1035" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1035" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1035" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1035" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1036" s="4"/>
+      <c r="B1036" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1036" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1036" s="6">
+        <v>46156.589583333334</v>
+      </c>
+      <c r="E1036" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1036" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1036" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1036" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1036" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1037" s="9"/>
+      <c r="B1037" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1037" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1037" s="11">
+        <v>46156.604861111111</v>
+      </c>
+      <c r="E1037" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1037" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1037" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1037" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1037" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1038" s="4"/>
+      <c r="B1038" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1038" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1038" s="6">
+        <v>46156.604861111111</v>
+      </c>
+      <c r="E1038" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1038" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1038" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1038" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1038" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1039" s="9"/>
+      <c r="B1039" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="C1039" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="D1039" s="11">
+        <v>46156.626388888886</v>
+      </c>
+      <c r="E1039" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1039" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1039" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1039" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1039" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1040" s="4"/>
+      <c r="B1040" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C1040" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D1040" s="6">
+        <v>46156.62777777778</v>
+      </c>
+      <c r="E1040" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1040" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1040" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1040" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1040" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1041" s="9"/>
+      <c r="B1041" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1041" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1041" s="11">
+        <v>46156.633333333331</v>
+      </c>
+      <c r="E1041" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1041" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1041" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1041" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1041" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1042" s="4"/>
+      <c r="B1042" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1042" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1042" s="6">
+        <v>46156.633333333331</v>
+      </c>
+      <c r="E1042" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1042" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1042" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1042" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1042" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1043" s="9"/>
+      <c r="B1043" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1043" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1043" s="11">
+        <v>46156.633333333331</v>
+      </c>
+      <c r="E1043" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1043" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1043" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1043" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1043" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1044" s="4"/>
+      <c r="B1044" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1044" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1044" s="6">
+        <v>46156.633333333331</v>
+      </c>
+      <c r="E1044" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1044" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1044" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1044" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1044" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1045" s="9"/>
+      <c r="B1045" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1045" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1045" s="11">
+        <v>46156.634722222225</v>
+      </c>
+      <c r="E1045" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1045" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1045" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1045" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1045" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1046" s="4"/>
+      <c r="B1046" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1046" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1046" s="6">
+        <v>46156.634722222225</v>
+      </c>
+      <c r="E1046" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1046" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1046" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1046" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1046" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1047" s="9"/>
+      <c r="B1047" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1047" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1047" s="11">
+        <v>46156.635416666664</v>
+      </c>
+      <c r="E1047" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1047" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1047" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1047" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1047" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1048" s="4"/>
+      <c r="B1048" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1048" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1048" s="6">
+        <v>46156.635416666664</v>
+      </c>
+      <c r="E1048" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1048" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1048" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1048" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1048" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1049" s="9"/>
+      <c r="B1049" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1049" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1049" s="11">
+        <v>46156.643055555556</v>
+      </c>
+      <c r="E1049" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1049" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1049" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1049" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1049" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1050" s="4"/>
+      <c r="B1050" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1050" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1050" s="6">
+        <v>46156.643055555556</v>
+      </c>
+      <c r="E1050" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1050" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1050" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1050" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1050" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1051" s="9"/>
+      <c r="B1051" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1051" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1051" s="11">
+        <v>46156.697916666664</v>
+      </c>
+      <c r="E1051" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1051" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1051" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1051" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1051" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1052" s="4"/>
+      <c r="B1052" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1052" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1052" s="6">
+        <v>46156.698611111111</v>
+      </c>
+      <c r="E1052" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1052" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1052" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1052" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1052" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1053" s="9"/>
+      <c r="B1053" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1053" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1053" s="11">
+        <v>46156.698611111111</v>
+      </c>
+      <c r="E1053" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1053" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1053" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1053" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1053" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1054" s="4"/>
+      <c r="B1054" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1054" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1054" s="6">
+        <v>46156.708333333336</v>
+      </c>
+      <c r="E1054" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1054" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1054" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1054" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1054" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1055" s="9"/>
+      <c r="B1055" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1055" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1055" s="11">
+        <v>46156.713194444441</v>
+      </c>
+      <c r="E1055" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1055" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1055" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1055" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1055" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1056" s="4"/>
+      <c r="B1056" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1056" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1056" s="6">
+        <v>46156.715277777781</v>
+      </c>
+      <c r="E1056" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1056" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1056" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1056" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1056" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1057" s="9"/>
+      <c r="B1057" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1057" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1057" s="11">
+        <v>46156.715277777781</v>
+      </c>
+      <c r="E1057" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1057" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1057" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1057" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1057" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1058" s="4"/>
+      <c r="B1058" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1058" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1058" s="6">
+        <v>46156.715277777781</v>
+      </c>
+      <c r="E1058" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1058" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1058" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1058" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1058" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1059" s="9"/>
+      <c r="B1059" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1059" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1059" s="11">
+        <v>46156.715277777781</v>
+      </c>
+      <c r="E1059" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1059" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1059" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1059" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1059" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1060" s="4"/>
+      <c r="B1060" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1060" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D1060" s="6">
+        <v>46156.745138888888</v>
+      </c>
+      <c r="E1060" s="7">
+        <v>46156</v>
+      </c>
+      <c r="F1060" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1060" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1060" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1060" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1061" s="9"/>
+      <c r="B1061" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1061" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="D1061" s="11">
+        <v>46156.748611111114</v>
+      </c>
+      <c r="E1061" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F1061" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1061" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1061" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1061" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1062" s="4"/>
+      <c r="B1062" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1062" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="D1062" s="6">
+        <v>46157.294444444444</v>
+      </c>
+      <c r="E1062" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1062" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1062" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1062" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1062" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1063" s="9"/>
+      <c r="B1063" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1063" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1063" s="11">
+        <v>46157.438888888886</v>
+      </c>
+      <c r="E1063" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1063" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1063" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1063" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1063" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1064" s="4"/>
+      <c r="B1064" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1064" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1064" s="6">
+        <v>46157.443055555559</v>
+      </c>
+      <c r="E1064" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1064" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1064" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1064" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1064" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1065" s="9"/>
+      <c r="B1065" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1065" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1065" s="11">
+        <v>46157.443055555559</v>
+      </c>
+      <c r="E1065" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1065" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1065" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1065" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1065" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1066" s="4"/>
+      <c r="B1066" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1066" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1066" s="6">
+        <v>46157.45208333333</v>
+      </c>
+      <c r="E1066" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1066" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1066" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1066" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1066" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1067" s="9"/>
+      <c r="B1067" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1067" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="D1067" s="11">
+        <v>46157.487500000003</v>
+      </c>
+      <c r="E1067" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1067" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1067" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1067" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1067" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1068" s="4"/>
+      <c r="B1068" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1068" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D1068" s="6">
+        <v>46157.487500000003</v>
+      </c>
+      <c r="E1068" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1068" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1068" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1068" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1068" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1069" s="9"/>
+      <c r="B1069" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1069" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="D1069" s="11">
+        <v>46157.488194444442</v>
+      </c>
+      <c r="E1069" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1069" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1069" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1069" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1069" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1070" s="4"/>
+      <c r="B1070" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1070" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D1070" s="6">
+        <v>46157.488194444442</v>
+      </c>
+      <c r="E1070" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1070" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1070" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1070" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1070" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1071" s="9"/>
+      <c r="B1071" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1071" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D1071" s="11">
+        <v>46157.492361111108</v>
+      </c>
+      <c r="E1071" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1071" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1071" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1071" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1071" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1072" s="4"/>
+      <c r="B1072" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1072" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D1072" s="6">
+        <v>46157.494444444441</v>
+      </c>
+      <c r="E1072" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1072" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1072" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1072" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1072" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1073" s="9"/>
+      <c r="B1073" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1073" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D1073" s="11">
+        <v>46157.529166666667</v>
+      </c>
+      <c r="E1073" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1073" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1073" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1073" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1073" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1074" s="4"/>
+      <c r="B1074" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1074" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1074" s="6">
+        <v>46157.609722222223</v>
+      </c>
+      <c r="E1074" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1074" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1074" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1074" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1074" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1075" s="9"/>
+      <c r="B1075" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1075" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1075" s="11">
+        <v>46157.609722222223</v>
+      </c>
+      <c r="E1075" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1075" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1075" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1075" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1075" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1076" s="4"/>
+      <c r="B1076" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1076" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1076" s="6">
+        <v>46157.61041666667</v>
+      </c>
+      <c r="E1076" s="7">
+        <v>46157</v>
+      </c>
+      <c r="F1076" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1076" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1076" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1076" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1077" s="9"/>
+      <c r="B1077" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1077" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1077" s="11">
+        <v>46157.629861111112</v>
+      </c>
+      <c r="E1077" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F1077" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1077" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1077" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1077" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
